--- a/src/test/resources/Excel/Data.xlsx
+++ b/src/test/resources/Excel/Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkarthik1\Desktop\Automation\SDET_Automation\Eclipse\Selenium\src\test\resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9F53A6-F429-44A0-AAA8-66890E37B522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A42553A-05A1-49F3-B3C5-5BF6B9668B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Username</t>
   </si>
@@ -28,26 +28,75 @@
     <t>Password</t>
   </si>
   <si>
-    <t>Karthik</t>
-  </si>
-  <si>
-    <t>kar1234</t>
-  </si>
-  <si>
-    <t>Hello</t>
-  </si>
-  <si>
     <t>UpdateMessage</t>
+  </si>
+  <si>
+    <t>TestCase</t>
+  </si>
+  <si>
+    <t>TC1</t>
+  </si>
+  <si>
+    <t>TC2</t>
+  </si>
+  <si>
+    <t>TC3</t>
+  </si>
+  <si>
+    <t>TC4</t>
+  </si>
+  <si>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>Pass1</t>
+  </si>
+  <si>
+    <t>Pass2</t>
+  </si>
+  <si>
+    <t>Pass3</t>
+  </si>
+  <si>
+    <t>Pass4</t>
+  </si>
+  <si>
+    <t>Message1</t>
+  </si>
+  <si>
+    <t>Message2</t>
+  </si>
+  <si>
+    <t>Message3</t>
+  </si>
+  <si>
+    <t>Message4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -354,35 +403,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="13.1796875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>